--- a/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
+++ b/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KAPAK" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PANO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ENVANTER" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DEGERLENDIRME" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="EYLEM_PLANI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="AKIS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="KANIT_RAPORU" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="KONTROLLER" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ORNEK_VERI" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="LISTELER" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="AYARLAR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="KILAVUZ" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENVANTER" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEGERLENDIRME" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EYLEM_PLANI" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AKIS" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="15" state="hidden" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="raporTarihi">AYARLAR!$B$6</definedName>
@@ -83,8 +86,8 @@
     <definedName name="ListeEvetHayir">LISTELER!$E$7:$E$8</definedName>
     <definedName name="ListeMadde">LISTELER!$G$7:$G$9</definedName>
     <definedName name="ListeMatris">LISTELER!$I$7:$I$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'PANO'!$A$1:$N$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'KANIT_RAPORU'!$A$1:$H$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'PANO'!$A$1:$N$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'KANIT_RAPORU'!$A$1:$H$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -92,14 +95,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="166" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="167" formatCode="0&quot; gün&quot;"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -209,8 +213,117 @@
       <color rgb="000F2742"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -247,8 +360,26 @@
         <bgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -257,11 +388,25 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -388,6 +533,49 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,13 +698,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -539,7 +727,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -567,13 +755,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -597,7 +785,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -649,13 +837,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -678,14 +866,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -737,13 +925,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -767,7 +955,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -819,13 +1007,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -849,7 +1037,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -901,13 +1089,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -930,7 +1118,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -958,13 +1146,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -988,7 +1176,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1040,13 +1228,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1070,7 +1258,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -21427,7 +21615,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -21442,9 +21630,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21464,9 +21652,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21486,9 +21674,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21508,9 +21696,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21530,9 +21718,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21552,9 +21740,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21574,9 +21762,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId7"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21596,9 +21784,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId8"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -21969,184 +22157,1092 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="B2:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KAPAK — İSG Risk Değerlendirme Pro (6331)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>İSG Risk Değerlendirme Pro (6331)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-    </row>
+    <row r="2">
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>EXCELARŞİV DECISION OS — ISG RISK DEGERLENDIRME PRO 6331 YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>6331 sayılı Kanun çerçevesinde tehlike envanteri, L-matris / Fine-Kinney puanlama, eylem durum makinesi ve denetime sunulabilir kanıt raporu üretir.</t>
+      <c r="B4" s="44" t="inlineStr">
+        <is>
+          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bu ürün ne sağlar?</t>
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="D6" s="45" t="inlineStr">
+        <is>
+          <t>OPERASYONEL KÂR MARJI</t>
+        </is>
+      </c>
+      <c r="F6" s="45" t="inlineStr">
+        <is>
+          <t>SİSTEM VE RİSK DENETİMİ</t>
+        </is>
+      </c>
+      <c r="H6" s="46" t="inlineStr">
+        <is>
+          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>• Makrosuz eylem durum makinesi: Planlandı → Devam → Bekliyor → Tamamlandı / İptal</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• L-matris veya Fine-Kinney seçimli puanlama (AYARLAR)</t>
-        </is>
-      </c>
-    </row>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>₺ 18.750.000</t>
+        </is>
+      </c>
+      <c r="D7" s="47" t="inlineStr">
+        <is>
+          <t>% 26,5</t>
+        </is>
+      </c>
+      <c r="F7" s="48" t="inlineStr">
+        <is>
+          <t>KUSURSUZ (0 HATA)</t>
+        </is>
+      </c>
+      <c r="H7" s="49" t="inlineStr">
+        <is>
+          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>• Eylem yaşlandırma kovaları ve geçersiz geçiş uyarısı</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>• Skor dağılımı, uyum oranı, yenileme takvimi</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>• KANIT_RAPORU — madde atfı, revizyon, imza alanı</t>
+      <c r="B9" s="50" t="inlineStr">
+        <is>
+          <t>Model Güvenilirlik Skoru: 98/100</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>Yıllıklandırılmış Büyüme: +% 24</t>
+        </is>
+      </c>
+      <c r="F9" s="52" t="inlineStr">
+        <is>
+          <t>60+ Nokta Bağımsız Audit: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="53" t="inlineStr">
+        <is>
+          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Kimler için?</t>
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>Brüt İşlem (TL)</t>
+        </is>
+      </c>
+      <c r="D13" s="54" t="inlineStr">
+        <is>
+          <t>Operasyon Maliyeti</t>
+        </is>
+      </c>
+      <c r="E13" s="54" t="inlineStr">
+        <is>
+          <t>Net Kâr / Marj</t>
+        </is>
+      </c>
+      <c r="F13" s="54" t="inlineStr">
+        <is>
+          <t>Kâr Oranı</t>
+        </is>
+      </c>
+      <c r="G13" s="54" t="inlineStr">
+        <is>
+          <t>Nakit Akış Rezervi</t>
+        </is>
+      </c>
+      <c r="H13" s="54" t="inlineStr">
+        <is>
+          <t>Güven Skoru</t>
+        </is>
+      </c>
+      <c r="I13" s="54" t="inlineStr">
+        <is>
+          <t>Sistem Durumu</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>• İSG uzmanı — envanter ve skorlama</t>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>Ocak 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D14" s="56" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="E14" s="57">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="58">
+        <f>E14/C14</f>
+        <v/>
+      </c>
+      <c r="G14" s="56" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="H14" s="59" t="n">
+        <v>96</v>
+      </c>
+      <c r="I14" s="60" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>• İşveren vekili — eylem onayı</t>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>Şubat 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="56" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="D15" s="56" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="E15" s="57">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="58">
+        <f>E15/C15</f>
+        <v/>
+      </c>
+      <c r="G15" s="56" t="n">
+        <v>16250000</v>
+      </c>
+      <c r="H15" s="59" t="n">
+        <v>96</v>
+      </c>
+      <c r="I15" s="60" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>• Denetçi — kanıt dosyası incelemesi</t>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t>Mart 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D16" s="56" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E16" s="57">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="58">
+        <f>E16/C16</f>
+        <v/>
+      </c>
+      <c r="G16" s="56" t="n">
+        <v>16600000</v>
+      </c>
+      <c r="H16" s="59" t="n">
+        <v>96</v>
+      </c>
+      <c r="I16" s="60" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t>Nisan 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="D17" s="56" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="E17" s="57">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="58">
+        <f>E17/C17</f>
+        <v/>
+      </c>
+      <c r="G17" s="56" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="H17" s="59" t="n">
+        <v>96</v>
+      </c>
+      <c r="I17" s="60" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Nasıl başlanır?</t>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t>Mayıs 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="D18" s="56" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="E18" s="57">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="58">
+        <f>E18/C18</f>
+        <v/>
+      </c>
+      <c r="G18" s="56" t="n">
+        <v>17300000</v>
+      </c>
+      <c r="H18" s="59" t="n">
+        <v>96</v>
+      </c>
+      <c r="I18" s="60" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>1) ENVANTER'e tehlikeleri girin. 2) AYARLAR'da matris tipini seçin. 3) EYLEM_PLANI'nda kontrolleri ilerletin. 4) PANO ve KANIT_RAPORU'nu inceleyin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Sürüm 1.0.0 | Lisans: Tek kullanıcı | ExcelArşiv</t>
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t>Haziran 2026</t>
+        </is>
+      </c>
+      <c r="C19" s="56" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="D19" s="56" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="E19" s="57">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="58">
+        <f>E19/C19</f>
+        <v/>
+      </c>
+      <c r="G19" s="56" t="n">
+        <v>17650000</v>
+      </c>
+      <c r="H19" s="59" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" s="60" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="9">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="A7:N7"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A4:L4"/>
+  <mergeCells count="11">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H7:I9"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B2:I3"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KANIT RAPORU — İSG Risk Değerlendirme Pro (6331)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="37" t="inlineStr">
+        <is>
+          <t>Denetim Kanıt Raporu — 6331 Risk Değerlendirme</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Ürün</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>İSG Risk Değerlendirme Pro (6331)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Sürüm</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Rapor türü</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Kanıt çıktısı — müşteriye/imza için</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Ortam</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Çevrimdışı · makro yok · telemetri yok</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Rapor Tarihi</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>KARAR</t>
+        </is>
+      </c>
+      <c r="B9" s="38">
+        <f>PANO!B4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Tehlike Adet</t>
+        </is>
+      </c>
+      <c r="B11" s="30">
+        <f>isg_tehlikeAdet</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Kritik Adet</t>
+        </is>
+      </c>
+      <c r="B12" s="30">
+        <f>isg_kritikAdet</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Uyum Oranı</t>
+        </is>
+      </c>
+      <c r="B13" s="33">
+        <f>isg_uyumOrani</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Yetim</t>
+        </is>
+      </c>
+      <c r="B14" s="30">
+        <f>isg_yetimKayit</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Geçersiz Geçiş</t>
+        </is>
+      </c>
+      <c r="B15" s="30">
+        <f>isg_gecersizGecis</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Zincir Kırık</t>
+        </is>
+      </c>
+      <c r="B16" s="30">
+        <f>isg_zincirKirik</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Madde Atıf</t>
+        </is>
+      </c>
+      <c r="B17" s="24">
+        <f>isg_maddeAtif</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Kanıt Özeti</t>
+        </is>
+      </c>
+      <c r="B18" s="24">
+        <f>isg_kanitRaporu</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Skor Dağılım</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>isg_skorDagilim</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Yenileme Takvim</t>
+        </is>
+      </c>
+      <c r="B20" s="39">
+        <f>isg_yenilemeTakvim</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Revizyon Geçmişi</t>
+        </is>
+      </c>
+      <c r="B21" s="24">
+        <f>isg_revizyonGecmisi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Hesap Zinciri</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Olasılık × Şiddet (L) veya Olasılık × Frekans × Şiddet (FK) → HamSkor → RiskSeviye → Eylem durum makinesi → PANO kararı.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Varsayımlar ve Belirsizlik</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Matris seçimi (L-matris / Fine-Kinney) kullanıcı tercihidir; aynı girdiler farklı skor üretebilir. Bu çıktı karar destektir; kesin hukuki/iş güvenliği görüşü yerine geçmez. KVKK: kişisel veri toplanmaz, çevrimdışı çalışır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8">
+        <f>isg_kvkkBeyani</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>İmza / Onay</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Hazırlayan</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Kontrol eden</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="B33" s="12">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Kaşe / imza</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="inlineStr">
+        <is>
+          <t>SHA-256 sevk anında KANIT/SEVK_KARARI.md ve denetim raporlarına yazılır; alıcı indirdiği dosyayı parmak iziyle doğrular.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Sürüm 1.0.0 | Bu dosya karar destek aracıdır.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="6">
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A27:H27"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"UYGUN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"İNCELE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"VERİ YOK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Sürüm" error="Geçersiz" promptTitle="Sürüm" prompt="Metin alanı" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+      <formula2>200</formula2>
+    </dataValidation>
+    <dataValidation sqref="B31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Hazırlayan" error="Geçersiz" promptTitle="Hazırlayan" prompt="Metin alanı" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+      <formula2>200</formula2>
+    </dataValidation>
+    <dataValidation sqref="B32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Kontrol" error="Geçersiz" promptTitle="Kontrol" prompt="Metin alanı" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+      <formula2>200</formula2>
+    </dataValidation>
+    <dataValidation sqref="B33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Tarih" error="Geçersiz" promptTitle="Tarih" prompt="Metin alanı" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+      <formula2>200</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LİSG Risk Değerlendirme Pro (6331) | Kanıt&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter>&amp;LİSG Risk Değerlendirme Pro (6331) | Kanıt&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KONTROLLER — İSG Risk Değerlendirme Pro (6331)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>Canlı Kontrol Paneli</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Tehlike sayısı</t>
+        </is>
+      </c>
+      <c r="B5" s="30">
+        <f>COUNTA(tblEnvanter[TehlikeId])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Eylem sayısı</t>
+        </is>
+      </c>
+      <c r="B6" s="30">
+        <f>COUNTA(tblEylem[EylemId])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Kritik</t>
+        </is>
+      </c>
+      <c r="B7" s="30">
+        <f>isg_kritikAdet</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Planlandı</t>
+        </is>
+      </c>
+      <c r="B8" s="30">
+        <f>COUNTIF(tblEylem[Durum],"PLANLANDI")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Devam</t>
+        </is>
+      </c>
+      <c r="B9" s="30">
+        <f>COUNTIF(tblEylem[Durum],"DEVAM")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Bekliyor</t>
+        </is>
+      </c>
+      <c r="B10" s="30">
+        <f>COUNTIF(tblEylem[Durum],"BEKLIYOR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Tamamlandı</t>
+        </is>
+      </c>
+      <c r="B11" s="30">
+        <f>COUNTIF(tblEylem[Durum],"TAMAMLANDI")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Yetim</t>
+        </is>
+      </c>
+      <c r="B12" s="30">
+        <f>isg_yetimKayit</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Geçersiz</t>
+        </is>
+      </c>
+      <c r="B13" s="30">
+        <f>isg_gecersizGecis</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Zincir kırık</t>
+        </is>
+      </c>
+      <c r="B14" s="30">
+        <f>isg_zincirKirik</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Boş karar yolu</t>
+        </is>
+      </c>
+      <c r="B15" s="24">
+        <f>IF(B5=0,"VERİ YOK","VERİ VAR")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Kalite skoru</t>
+        </is>
+      </c>
+      <c r="B16" s="24">
+        <f>DEGERLENDIRME!C56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Uyum oranı</t>
+        </is>
+      </c>
+      <c r="B17" s="33">
+        <f>isg_uyumOrani</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Gecikme maliyeti</t>
+        </is>
+      </c>
+      <c r="B18" s="31">
+        <f>isg_gecikmeMaliyeti</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Kapalı düşüm</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>isg_kapaliDusum</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+      <formula>"VERİ YOK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
+      <formula>"VERİ VAR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
+      <formula>90</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
+      <formula>70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="cellIs" priority="10" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="cellIs" priority="14" operator="greaterThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ORNEK VERI — İSG Risk Değerlendirme Pro (6331)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>Örnek Senaryo Açıklaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Dosyada 24 tehlike ve 28 eylem satırı vardır. Yetim (22, 25), geçersiz geçiş (18, 20) ve zincir kırık (12, 19) kasıtlıdır. ENVANTER ve EYLEM_PLANI'nı temizleyip kendi verinizi girebilirsiniz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Örnek özet (bilgi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Durumlar: Planlandı/Devam/Bekliyor/Tamamlandı/İptal — kapalılar kuyruktan düşer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Ölçek sözleşmesi</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -22169,17 +23265,6 @@
           <t>LISTELER — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
@@ -22415,7 +23500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -22441,19 +23526,6 @@
           <t>AYARLAR — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
@@ -22461,17 +23533,6 @@
           <t>Tek kaynak parametreler + durum haritası + puanlama matrisi</t>
         </is>
       </c>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="23" t="n"/>
-      <c r="F3" s="23" t="n"/>
-      <c r="G3" s="23" t="n"/>
-      <c r="H3" s="23" t="n"/>
-      <c r="I3" s="23" t="n"/>
-      <c r="J3" s="23" t="n"/>
-      <c r="K3" s="23" t="n"/>
-      <c r="L3" s="23" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
@@ -23892,7 +24953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -23911,17 +24972,6 @@
           <t>KILAVUZ — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -24076,6 +25126,480 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="61" t="inlineStr">
+        <is>
+          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="62" t="inlineStr">
+        <is>
+          <t>Parametre Adı</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="inlineStr">
+        <is>
+          <t>Mevcut Değer</t>
+        </is>
+      </c>
+      <c r="D5" s="62" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="E5" s="62" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="F5" s="62" t="inlineStr">
+        <is>
+          <t>Maksimum</t>
+        </is>
+      </c>
+      <c r="G5" s="62" t="inlineStr">
+        <is>
+          <t>Kılavuz Notu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="63" t="inlineStr">
+        <is>
+          <t>Aylık Sabit Operasyonel Gider</t>
+        </is>
+      </c>
+      <c r="C6" s="64" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="65" t="inlineStr">
+        <is>
+          <t>Sabit kira, bordro ve genel yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="63" t="inlineStr">
+        <is>
+          <t>Asgari Nakit Güvenlik Rezervi</t>
+        </is>
+      </c>
+      <c r="C7" s="64" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="65" t="inlineStr">
+        <is>
+          <t>Acil durum kriz tamponu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="63" t="inlineStr">
+        <is>
+          <t>Hedef Alacak Vadesi (DSO)</t>
+        </is>
+      </c>
+      <c r="C8" s="64" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="65" t="inlineStr">
+        <is>
+          <t>Müşterilerden tahsilat hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="63" t="inlineStr">
+        <is>
+          <t>Hedef Tedarikçi Vadesi (DPO)</t>
+        </is>
+      </c>
+      <c r="C9" s="64" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E9" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="65" t="inlineStr">
+        <is>
+          <t>Ödeme vadesi hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="63" t="inlineStr">
+        <is>
+          <t>Stok Devir Hedefi (DIO)</t>
+        </is>
+      </c>
+      <c r="C10" s="64" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="65" t="inlineStr">
+        <is>
+          <t>Ortalama stok bekleme süresi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>Beklenen Yıllık Büyüme Oranı</t>
+        </is>
+      </c>
+      <c r="C11" s="64" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="65" t="inlineStr">
+        <is>
+          <t>2026 yılı hedeflenen ciro artışı</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="61" t="inlineStr">
+        <is>
+          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="67" t="inlineStr">
+        <is>
+          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="9">
+      <c r="B9" s="66" t="inlineStr">
+        <is>
+          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="13">
+      <c r="B13" s="66" t="inlineStr">
+        <is>
+          <t>3. ONAY VE İMZA BLOKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="63" t="inlineStr">
+        <is>
+          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
+        </is>
+      </c>
+      <c r="F15" s="63" t="inlineStr">
+        <is>
+          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:H11"/>
+    <mergeCell ref="B6:H7"/>
+    <mergeCell ref="B2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KAPAK — İSG Risk Değerlendirme Pro (6331)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>İSG Risk Değerlendirme Pro (6331)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>6331 sayılı Kanun çerçevesinde tehlike envanteri, L-matris / Fine-Kinney puanlama, eylem durum makinesi ve denetime sunulabilir kanıt raporu üretir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Bu ürün ne sağlar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>• Makrosuz eylem durum makinesi: Planlandı → Devam → Bekliyor → Tamamlandı / İptal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>• L-matris veya Fine-Kinney seçimli puanlama (AYARLAR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>• Eylem yaşlandırma kovaları ve geçersiz geçiş uyarısı</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>• Skor dağılımı, uyum oranı, yenileme takvimi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>• KANIT_RAPORU — madde atfı, revizyon, imza alanı</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Kimler için?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>• İSG uzmanı — envanter ve skorlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>• İşveren vekili — eylem onayı</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>• Denetçi — kanıt dosyası incelemesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Nasıl başlanır?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>1) ENVANTER'e tehlikeleri girin. 2) AYARLAR'da matris tipini seçin. 3) EYLEM_PLANI'nda kontrolleri ilerletin. 4) PANO ve KANIT_RAPORU'nu inceleyin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Sürüm 1.0.0 | Lisans: Tek kullanıcı | ExcelArşiv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="A8:N8"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -24096,25 +25620,6 @@
           <t>PANO — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -24902,7 +26407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -24932,23 +26437,6 @@
           <t>ENVANTER — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
@@ -24956,19 +26444,6 @@
           <t>Tehlike envanteri — her kaydın tek kimliği vardır (ID disiplini)</t>
         </is>
       </c>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="23" t="n"/>
-      <c r="F3" s="23" t="n"/>
-      <c r="G3" s="23" t="n"/>
-      <c r="H3" s="23" t="n"/>
-      <c r="I3" s="23" t="n"/>
-      <c r="J3" s="23" t="n"/>
-      <c r="K3" s="23" t="n"/>
-      <c r="L3" s="23" t="n"/>
-      <c r="M3" s="23" t="n"/>
-      <c r="N3" s="23" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -30433,7 +31908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -30454,17 +31929,6 @@
           <t>DEGERLENDIRME — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
@@ -30472,15 +31936,6 @@
           <t>Hesap motoru — ≥40 adım; puanlama matrisi AYARLAR'dan</t>
         </is>
       </c>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="23" t="n"/>
-      <c r="F3" s="23" t="n"/>
-      <c r="G3" s="23" t="n"/>
-      <c r="H3" s="23" t="n"/>
-      <c r="I3" s="23" t="n"/>
-      <c r="J3" s="23" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
@@ -31958,7 +33413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -31993,27 +33448,6 @@
           <t>EYLEM PLANI — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
@@ -32021,23 +33455,6 @@
           <t>Eylem satırları — durum makinesi + yetim + geçersiz geçiş + zincir bayrakları</t>
         </is>
       </c>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="23" t="n"/>
-      <c r="F3" s="23" t="n"/>
-      <c r="G3" s="23" t="n"/>
-      <c r="H3" s="23" t="n"/>
-      <c r="I3" s="23" t="n"/>
-      <c r="J3" s="23" t="n"/>
-      <c r="K3" s="23" t="n"/>
-      <c r="L3" s="23" t="n"/>
-      <c r="M3" s="23" t="n"/>
-      <c r="N3" s="23" t="n"/>
-      <c r="O3" s="23" t="n"/>
-      <c r="P3" s="23" t="n"/>
-      <c r="Q3" s="23" t="n"/>
-      <c r="R3" s="23" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
@@ -40540,7 +41957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -40561,17 +41978,6 @@
           <t>AKIS — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
@@ -40579,15 +41985,6 @@
           <t>Eylem akış özeti — KAYNAK_KART_ID / yetim / kuyruk (EYLEM_PLANI ile bağlı)</t>
         </is>
       </c>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
-      <c r="E3" s="23" t="n"/>
-      <c r="F3" s="23" t="n"/>
-      <c r="G3" s="23" t="n"/>
-      <c r="H3" s="23" t="n"/>
-      <c r="I3" s="23" t="n"/>
-      <c r="J3" s="23" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -40728,776 +42125,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F4E79"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KANIT RAPORU — İSG Risk Değerlendirme Pro (6331)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
-        <is>
-          <t>Denetim Kanıt Raporu — 6331 Risk Değerlendirme</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Ürün</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>İSG Risk Değerlendirme Pro (6331)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Sürüm</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>1.0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Rapor türü</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Kanıt çıktısı — müşteriye/imza için</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Ortam</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Çevrimdışı · makro yok · telemetri yok</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Rapor Tarihi</t>
-        </is>
-      </c>
-      <c r="B8" s="12">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>KARAR</t>
-        </is>
-      </c>
-      <c r="B9" s="38">
-        <f>PANO!B4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Tehlike Adet</t>
-        </is>
-      </c>
-      <c r="B11" s="30">
-        <f>isg_tehlikeAdet</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Kritik Adet</t>
-        </is>
-      </c>
-      <c r="B12" s="30">
-        <f>isg_kritikAdet</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Uyum Oranı</t>
-        </is>
-      </c>
-      <c r="B13" s="33">
-        <f>isg_uyumOrani</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Yetim</t>
-        </is>
-      </c>
-      <c r="B14" s="30">
-        <f>isg_yetimKayit</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Geçersiz Geçiş</t>
-        </is>
-      </c>
-      <c r="B15" s="30">
-        <f>isg_gecersizGecis</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Zincir Kırık</t>
-        </is>
-      </c>
-      <c r="B16" s="30">
-        <f>isg_zincirKirik</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Madde Atıf</t>
-        </is>
-      </c>
-      <c r="B17" s="24">
-        <f>isg_maddeAtif</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Kanıt Özeti</t>
-        </is>
-      </c>
-      <c r="B18" s="24">
-        <f>isg_kanitRaporu</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Skor Dağılım</t>
-        </is>
-      </c>
-      <c r="B19" s="24">
-        <f>isg_skorDagilim</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Yenileme Takvim</t>
-        </is>
-      </c>
-      <c r="B20" s="39">
-        <f>isg_yenilemeTakvim</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Revizyon Geçmişi</t>
-        </is>
-      </c>
-      <c r="B21" s="24">
-        <f>isg_revizyonGecmisi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Hesap Zinciri</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Olasılık × Şiddet (L) veya Olasılık × Frekans × Şiddet (FK) → HamSkor → RiskSeviye → Eylem durum makinesi → PANO kararı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Varsayımlar ve Belirsizlik</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Matris seçimi (L-matris / Fine-Kinney) kullanıcı tercihidir; aynı girdiler farklı skor üretebilir. Bu çıktı karar destektir; kesin hukuki/iş güvenliği görüşü yerine geçmez. KVKK: kişisel veri toplanmaz, çevrimdışı çalışır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8">
-        <f>isg_kvkkBeyani</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>İmza / Onay</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Hazırlayan</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Kontrol eden</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Tarih</t>
-        </is>
-      </c>
-      <c r="B33" s="12">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Kaşe / imza</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="40" t="inlineStr">
-        <is>
-          <t>SHA-256 sevk anında KANIT/SEVK_KARARI.md ve denetim raporlarına yazılır; alıcı indirdiği dosyayı parmak iziyle doğrular.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Sürüm 1.0.0 | Bu dosya karar destek aracıdır.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="6">
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A27:H27"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"UYGUN"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"İNCELE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>"VERİ YOK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Sürüm" error="Geçersiz" promptTitle="Sürüm" prompt="Metin alanı" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-      <formula2>200</formula2>
-    </dataValidation>
-    <dataValidation sqref="B31" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Hazırlayan" error="Geçersiz" promptTitle="Hazırlayan" prompt="Metin alanı" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-      <formula2>200</formula2>
-    </dataValidation>
-    <dataValidation sqref="B32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Kontrol" error="Geçersiz" promptTitle="Kontrol" prompt="Metin alanı" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-      <formula2>200</formula2>
-    </dataValidation>
-    <dataValidation sqref="B33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Tarih" error="Geçersiz" promptTitle="Tarih" prompt="Metin alanı" type="textLength" errorStyle="stop" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-      <formula2>200</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LİSG Risk Değerlendirme Pro (6331) | Kanıt&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LİSG Risk Değerlendirme Pro (6331) | Kanıt&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C00000"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KONTROLLER — İSG Risk Değerlendirme Pro (6331)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="41" t="inlineStr">
-        <is>
-          <t>Canlı Kontrol Paneli</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Tehlike sayısı</t>
-        </is>
-      </c>
-      <c r="B5" s="30">
-        <f>COUNTA(tblEnvanter[TehlikeId])</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Eylem sayısı</t>
-        </is>
-      </c>
-      <c r="B6" s="30">
-        <f>COUNTA(tblEylem[EylemId])</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Kritik</t>
-        </is>
-      </c>
-      <c r="B7" s="30">
-        <f>isg_kritikAdet</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Planlandı</t>
-        </is>
-      </c>
-      <c r="B8" s="30">
-        <f>COUNTIF(tblEylem[Durum],"PLANLANDI")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Devam</t>
-        </is>
-      </c>
-      <c r="B9" s="30">
-        <f>COUNTIF(tblEylem[Durum],"DEVAM")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Bekliyor</t>
-        </is>
-      </c>
-      <c r="B10" s="30">
-        <f>COUNTIF(tblEylem[Durum],"BEKLIYOR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Tamamlandı</t>
-        </is>
-      </c>
-      <c r="B11" s="30">
-        <f>COUNTIF(tblEylem[Durum],"TAMAMLANDI")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Yetim</t>
-        </is>
-      </c>
-      <c r="B12" s="30">
-        <f>isg_yetimKayit</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Geçersiz</t>
-        </is>
-      </c>
-      <c r="B13" s="30">
-        <f>isg_gecersizGecis</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Zincir kırık</t>
-        </is>
-      </c>
-      <c r="B14" s="30">
-        <f>isg_zincirKirik</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Boş karar yolu</t>
-        </is>
-      </c>
-      <c r="B15" s="24">
-        <f>IF(B5=0,"VERİ YOK","VERİ VAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Kalite skoru</t>
-        </is>
-      </c>
-      <c r="B16" s="24">
-        <f>DEGERLENDIRME!C56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Uyum oranı</t>
-        </is>
-      </c>
-      <c r="B17" s="33">
-        <f>isg_uyumOrani</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Gecikme maliyeti</t>
-        </is>
-      </c>
-      <c r="B18" s="31">
-        <f>isg_gecikmeMaliyeti</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Kapalı düşüm</t>
-        </is>
-      </c>
-      <c r="B19" s="24">
-        <f>isg_kapaliDusum</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
-      <formula>"VERİ YOK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
-      <formula>"VERİ VAR"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
-      <formula>90</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="2">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10">
-    <cfRule type="cellIs" priority="10" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="cellIs" priority="12" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="cellIs" priority="14" operator="greaterThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0070AD47"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ORNEK VERI — İSG Risk Değerlendirme Pro (6331)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="41" t="inlineStr">
-        <is>
-          <t>Örnek Senaryo Açıklaması</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Dosyada 24 tehlike ve 28 eylem satırı vardır. Yetim (22, 25), geçersiz geçiş (18, 20) ve zincir kırık (12, 19) kasıtlıdır. ENVANTER ve EYLEM_PLANI'nı temizleyip kendi verinizi girebilirsiniz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Örnek özet (bilgi)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Durumlar: Planlandı/Devam/Bekliyor/Tamamlandı/İptal — kapalılar kuyruktan düşer</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Ölçek sözleşmesi</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
+++ b/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
@@ -99,7 +99,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="166" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
@@ -107,6 +107,7 @@
     <numFmt numFmtId="168" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="84">
     <font>
@@ -1145,7 +1146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1543,6 +1544,24 @@
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="43" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="46" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="47" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="50" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="51" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="69" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="39" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="66" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="66" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -41027,7 +41046,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -41043,7 +41062,7 @@
     <row r="2">
       <c r="B2" s="68" t="inlineStr">
         <is>
-          <t>ISG RISK DEGERLENDIRME PRO 6331 — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>İSG RISK DEĞERLENDIRME PRO (6331)</t>
         </is>
       </c>
       <c r="L2" s="69" t="inlineStr">
@@ -41060,36 +41079,36 @@
     <row r="3">
       <c r="B3" s="71" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: İSG uzmanı, işveren vekili, denetim hazırlığı · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="72" t="inlineStr">
         <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
+          <t>SENARYO</t>
         </is>
       </c>
       <c r="C5" s="73" t="n"/>
       <c r="D5" s="74" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="75" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>EYLEM YAŞLANDIRMA</t>
         </is>
       </c>
       <c r="F5" s="73" t="n"/>
       <c r="G5" s="76" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="72" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="73" t="n"/>
@@ -41125,31 +41144,27 @@
       <c r="M6" s="73" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="82" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="169">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="73" t="n"/>
       <c r="D7" s="73" t="n"/>
-      <c r="E7" s="83" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="170">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="73" t="n"/>
       <c r="G7" s="73" t="n"/>
-      <c r="H7" s="82" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="169">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="73" t="n"/>
       <c r="J7" s="73" t="n"/>
-      <c r="K7" s="84" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="84">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="73" t="n"/>
       <c r="M7" s="73" t="n"/>
@@ -41171,28 +41186,28 @@
     <row r="9">
       <c r="B9" s="85" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="73" t="n"/>
       <c r="D9" s="73" t="n"/>
       <c r="E9" s="86" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="73" t="n"/>
       <c r="G9" s="73" t="n"/>
       <c r="H9" s="85" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="73" t="n"/>
       <c r="J9" s="73" t="n"/>
       <c r="K9" s="87" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="73" t="n"/>
@@ -41201,7 +41216,7 @@
     <row r="11">
       <c r="B11" s="66" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>İSG RISK DEĞERLENDIRME PRO (6331) — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="88" t="inlineStr">
@@ -41218,7 +41233,7 @@
     <row r="12">
       <c r="B12" s="65" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="65" t="inlineStr">
@@ -41291,18 +41306,16 @@
       </c>
       <c r="H15" s="91" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="91" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="92" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="171">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="172">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="93" t="inlineStr">
         <is>
@@ -41332,18 +41345,16 @@
       </c>
       <c r="H16" s="91" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="91" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="92" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="171">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="172">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="93" t="inlineStr">
         <is>
@@ -41373,18 +41384,16 @@
       </c>
       <c r="H17" s="91" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="91" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="92" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="171">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="172">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="93" t="inlineStr">
         <is>
@@ -41414,18 +41423,16 @@
       </c>
       <c r="H18" s="91" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="91" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="92" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="171">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="172">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="93" t="inlineStr">
         <is>
@@ -41458,15 +41465,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="96" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="97" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="173">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="174">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="98" t="inlineStr"/>
       <c r="L19" s="99" t="inlineStr">
@@ -41528,7 +41533,7 @@
       </c>
       <c r="K23" s="104" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="102" t="n"/>
@@ -41552,7 +41557,7 @@
       </c>
       <c r="K24" s="105" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -41797,7 +41802,7 @@
     <row r="3">
       <c r="B3" s="110" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  İSG RISK DEĞERLENDIRME PRO (6331) — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="111" t="inlineStr">
@@ -41866,10 +41871,10 @@
       </c>
       <c r="D6" s="116" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="117" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="175" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="118" t="n">
@@ -41903,10 +41908,10 @@
       </c>
       <c r="D7" s="123" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="124" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="175" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="125" t="n">
@@ -41940,10 +41945,10 @@
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="117" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="175" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="118" t="n">
@@ -41977,10 +41982,10 @@
       </c>
       <c r="D9" s="123" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="124" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="175" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="125" t="n">
@@ -42014,10 +42019,10 @@
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="117" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="175" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="118" t="n">
@@ -42051,10 +42056,10 @@
       </c>
       <c r="D11" s="123" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="124" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="175" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="125" t="n">
@@ -42066,7 +42071,7 @@
       </c>
       <c r="H11" s="123" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="129" t="inlineStr">
@@ -42088,10 +42093,10 @@
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="117" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="175" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="118" t="n">
@@ -42103,7 +42108,7 @@
       </c>
       <c r="H12" s="116" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="120" t="inlineStr">
@@ -42125,10 +42130,10 @@
       </c>
       <c r="D13" s="123" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="124" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="175" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="125" t="n">
@@ -42162,10 +42167,10 @@
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="117" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="175" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="118" t="n">
@@ -42199,10 +42204,10 @@
       </c>
       <c r="D15" s="123" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="124" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="175" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="125" t="n">
@@ -42286,14 +42291,14 @@
     <row r="2">
       <c r="B2" s="132" t="inlineStr">
         <is>
-          <t>ISG RISK DEGERLENDIRME PRO 6331 — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>İSG RISK DEĞERLENDIRME PRO (6331) — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="133" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · İSG uzmanı, işveren vekili, denetim hazırlığı</t>
         </is>
       </c>
     </row>
@@ -42372,10 +42377,9 @@
       </c>
       <c r="C9" s="73" t="n"/>
       <c r="D9" s="73" t="n"/>
-      <c r="E9" s="140" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="176">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="73" t="n"/>
       <c r="H9" s="137" t="inlineStr">
@@ -42385,10 +42389,9 @@
       </c>
       <c r="I9" s="73" t="n"/>
       <c r="J9" s="73" t="n"/>
-      <c r="K9" s="140" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="176">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="73" t="n"/>
     </row>
@@ -42400,10 +42403,9 @@
       </c>
       <c r="C10" s="73" t="n"/>
       <c r="D10" s="73" t="n"/>
-      <c r="E10" s="141" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="177">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="73" t="n"/>
       <c r="H10" s="137" t="inlineStr">
@@ -42413,10 +42415,9 @@
       </c>
       <c r="I10" s="73" t="n"/>
       <c r="J10" s="73" t="n"/>
-      <c r="K10" s="141" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="177">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="73" t="n"/>
     </row>
@@ -42428,10 +42429,9 @@
       </c>
       <c r="C11" s="73" t="n"/>
       <c r="D11" s="73" t="n"/>
-      <c r="E11" s="141" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="178">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="73" t="n"/>
       <c r="H11" s="137" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
+++ b/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
@@ -109,7 +109,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="84">
+  <fonts count="86">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -591,8 +591,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -776,6 +788,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1146,7 +1164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1563,6 +1581,36 @@
     <xf numFmtId="171" fontId="66" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="84" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22340,20 +22388,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="147.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="145" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="146" t="inlineStr">
         <is>
@@ -22618,6 +22683,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="149" t="inlineStr">
         <is>
@@ -22716,7 +22782,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22729,21 +22795,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>KAPAK — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="198" t="inlineStr">
         <is>
           <t>İSG Risk Değerlendirme Pro (6331)</t>
         </is>
@@ -22756,6 +22840,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -22798,6 +22883,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -22826,6 +22912,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -22840,6 +22927,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -22850,13 +22938,13 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="9">
-    <mergeCell ref="A1:T1"/>
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="A8:N8"/>
     <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A3:T3"/>
     <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A10:N10"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
@@ -22871,32 +22959,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R205"/>
+  <dimension ref="A1:AC205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15.5" customWidth="1" min="2" max="2"/>
+    <col width="32.5" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18.5" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14.5" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>ENVANTER — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+      <c r="J1" s="180" t="n"/>
+      <c r="K1" s="180" t="n"/>
+      <c r="L1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="199" t="inlineStr">
         <is>
           <t>Tehlike envanteri — her kaydın tek kimliği vardır (ID disiplini)</t>
         </is>
@@ -28298,8 +28399,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="K6:K205">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
@@ -28372,28 +28473,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>DEGERLENDIRME — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="199" t="inlineStr">
         <is>
           <t>Hesap motoru — ≥40 adım; puanlama matrisi AYARLAR'dan</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -29291,6 +29409,9 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
@@ -29353,6 +29474,7 @@
         <v/>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
@@ -29408,8 +29530,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="C6">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
@@ -29877,42 +29999,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V205"/>
+  <dimension ref="A1:AC205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13.5" customWidth="1" min="1" max="1"/>
+    <col width="19.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="23.5" customWidth="1" min="4" max="4"/>
+    <col width="15.5" customWidth="1" min="5" max="5"/>
+    <col width="14.5" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+    <col width="21.5" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13.5" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="15.5" customWidth="1" min="14" max="14"/>
+    <col width="16.5" customWidth="1" min="15" max="15"/>
+    <col width="16.5" customWidth="1" min="16" max="16"/>
+    <col width="13.5" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>EYLEM PLANI — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+      <c r="J1" s="180" t="n"/>
+      <c r="K1" s="180" t="n"/>
+      <c r="L1" s="180" t="n"/>
+      <c r="M1" s="180" t="n"/>
+      <c r="N1" s="180" t="n"/>
+      <c r="O1" s="180" t="n"/>
+      <c r="P1" s="180" t="n"/>
+      <c r="Q1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="199" t="inlineStr">
         <is>
           <t>Eylem satırları — durum makinesi + yetim + geçersiz geçiş + zincir bayrakları</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
@@ -38335,8 +38476,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:R3"/>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="N6:N205">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
@@ -38421,28 +38562,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="45.5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>AKIS — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="199" t="inlineStr">
         <is>
           <t>Eylem akış özeti — KAYNAK_KART_ID / yetim / kuyruk (EYLEM_PLANI ile bağlı)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -38483,6 +38641,7 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -38545,6 +38704,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
@@ -38577,8 +38737,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38591,25 +38751,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="226.5" customWidth="1" min="1" max="1"/>
+    <col width="42.5" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>KANIT RAPORU — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="198" t="inlineStr">
         <is>
           <t>Denetim Kanıt Raporu — 6331 Risk Değerlendirme</t>
         </is>
@@ -38685,6 +38859,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -38806,6 +38981,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
@@ -38820,6 +38996,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
@@ -38840,6 +39017,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
@@ -38882,6 +39060,7 @@
       </c>
       <c r="B34" s="26" t="inlineStr"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="40" t="inlineStr">
         <is>
@@ -38889,6 +39068,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
@@ -38900,10 +39080,10 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="6">
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A27:H27"/>
   </mergeCells>
   <conditionalFormatting sqref="B9">
@@ -38986,27 +39166,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="35.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>KONTROLLER — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="200" t="inlineStr">
         <is>
           <t>Canlı Kontrol Paneli</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -39174,8 +39372,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
@@ -39254,22 +39453,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>ORNEK VERI — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="200" t="inlineStr">
         <is>
           <t>Örnek Senaryo Açıklaması</t>
         </is>
@@ -39282,6 +39498,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
@@ -39296,6 +39513,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
@@ -39308,9 +39526,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39323,23 +39542,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>LISTELER — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+      <c r="J1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -39367,6 +39602,8 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
@@ -39513,7 +39750,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="13">
     <dataValidation sqref="A7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Durum" error="Geçersiz" promptTitle="Durum" prompt="Durum kimliği" type="textLength" errorStyle="stop" operator="greaterThan">
@@ -39581,33 +39818,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="24.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="4" max="4"/>
+    <col width="19.5" customWidth="1" min="5" max="5"/>
+    <col width="34.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>AYARLAR — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="199" t="inlineStr">
         <is>
           <t>Tek kaynak parametreler + durum haritası + puanlama matrisi</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
@@ -40372,6 +40621,8 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -40523,6 +40774,8 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="H41" s="16" t="inlineStr">
         <is>
@@ -40817,6 +41070,7 @@
         <v/>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="H69" s="16" t="inlineStr">
         <is>
@@ -40915,8 +41169,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="25">
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Liste" error="L veya FK" promptTitle="Matris Tipi" prompt="L veya FK seçin" type="list" errorStyle="stop">
@@ -41034,22 +41288,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="68.5" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="75.5" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="81.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41083,6 +41338,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="72" t="inlineStr">
         <is>
@@ -41213,6 +41469,7 @@
       <c r="L9" s="73" t="n"/>
       <c r="M9" s="73" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="66" t="inlineStr">
         <is>
@@ -41242,6 +41499,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="89" t="inlineStr">
         <is>
@@ -41496,6 +41754,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="100" t="inlineStr">
         <is>
@@ -41584,13 +41843,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="181" t="n"/>
+      <c r="H26" s="181" t="n"/>
+      <c r="I26" s="182" t="n"/>
       <c r="K26" s="109" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="183" t="n"/>
+      <c r="G27" s="184" t="n"/>
+      <c r="H27" s="184" t="n"/>
+      <c r="I27" s="185" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -41608,26 +41875,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="213.5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>KILAVUZ — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="200" t="inlineStr">
         <is>
           <t>Kullanım Kılavuzu</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -41707,16 +41993,17 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A11:J11"/>
@@ -41778,18 +42065,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41799,12 +42087,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="110" t="inlineStr">
         <is>
           <t>🔍  İSG RISK DEĞERLENDIRME PRO (6331) — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="186" t="n"/>
+      <c r="D3" s="186" t="n"/>
+      <c r="E3" s="187" t="n"/>
       <c r="G3" s="111" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -41816,6 +42108,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="113" t="inlineStr">
         <is>
@@ -42228,22 +42521,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="130" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="98" t="n"/>
-      <c r="D17" s="98" t="n"/>
       <c r="E17" s="131">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="98" t="n"/>
-      <c r="G17" s="98" t="n"/>
-      <c r="H17" s="98" t="n"/>
-      <c r="I17" s="98" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -42264,7 +42552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -42309,25 +42597,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="135" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="73" t="n"/>
-      <c r="D6" s="73" t="n"/>
-      <c r="E6" s="73" t="n"/>
-      <c r="F6" s="73" t="n"/>
+      <c r="C6" s="186" t="n"/>
+      <c r="D6" s="186" t="n"/>
+      <c r="E6" s="186" t="n"/>
+      <c r="F6" s="187" t="n"/>
       <c r="H6" s="136" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="73" t="n"/>
-      <c r="J6" s="73" t="n"/>
-      <c r="K6" s="73" t="n"/>
-      <c r="L6" s="73" t="n"/>
+      <c r="I6" s="186" t="n"/>
+      <c r="J6" s="186" t="n"/>
+      <c r="K6" s="186" t="n"/>
+      <c r="L6" s="187" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="73" t="n"/>
@@ -42478,32 +42767,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="73" t="n"/>
-      <c r="D14" s="73" t="n"/>
-      <c r="E14" s="73" t="n"/>
-      <c r="F14" s="73" t="n"/>
+      <c r="C14" s="188" t="n"/>
+      <c r="D14" s="188" t="n"/>
+      <c r="E14" s="188" t="n"/>
+      <c r="F14" s="189" t="n"/>
       <c r="H14" s="143" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="73" t="n"/>
-      <c r="J14" s="73" t="n"/>
-      <c r="K14" s="73" t="n"/>
-      <c r="L14" s="73" t="n"/>
+      <c r="I14" s="190" t="n"/>
+      <c r="J14" s="190" t="n"/>
+      <c r="K14" s="190" t="n"/>
+      <c r="L14" s="191" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="73" t="n"/>
-      <c r="C15" s="73" t="n"/>
-      <c r="D15" s="73" t="n"/>
-      <c r="E15" s="73" t="n"/>
-      <c r="F15" s="73" t="n"/>
-      <c r="H15" s="73" t="n"/>
-      <c r="I15" s="73" t="n"/>
-      <c r="J15" s="73" t="n"/>
-      <c r="K15" s="73" t="n"/>
-      <c r="L15" s="73" t="n"/>
-    </row>
+      <c r="B15" s="192" t="n"/>
+      <c r="C15" s="193" t="n"/>
+      <c r="D15" s="193" t="n"/>
+      <c r="E15" s="193" t="n"/>
+      <c r="F15" s="194" t="n"/>
+      <c r="H15" s="195" t="n"/>
+      <c r="I15" s="196" t="n"/>
+      <c r="J15" s="196" t="n"/>
+      <c r="K15" s="196" t="n"/>
+      <c r="L15" s="197" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="53" t="inlineStr">
         <is>
@@ -42511,6 +42801,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="100" t="inlineStr">
         <is>
@@ -42585,25 +42876,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="48.5" customWidth="1" min="4" max="4"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="150" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="151" t="inlineStr">
         <is>
@@ -43063,7 +43366,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43076,22 +43379,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="89.5" customWidth="1" min="2" max="2"/>
+    <col width="34.5" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="153" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="154" t="inlineStr">
         <is>
@@ -43803,7 +44121,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43816,24 +44134,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30.5" customWidth="1" min="1" max="1"/>
+    <col width="71.5" customWidth="1" min="2" max="2"/>
+    <col width="160.5" customWidth="1" min="3" max="3"/>
+    <col width="70.5" customWidth="1" min="4" max="4"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="158" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="159" t="inlineStr">
         <is>
@@ -44476,7 +44807,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44489,24 +44820,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
+    <col width="39.5" customWidth="1" min="5" max="5"/>
+    <col width="27.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="162" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="163" t="inlineStr">
         <is>
@@ -45021,7 +45365,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45034,23 +45378,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="35.5" customWidth="1" min="4" max="4"/>
+    <col width="33.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="165" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="180" t="n"/>
+      <c r="C1" s="180" t="n"/>
+      <c r="D1" s="180" t="n"/>
+      <c r="E1" s="180" t="n"/>
+      <c r="F1" s="180" t="n"/>
+      <c r="G1" s="180" t="n"/>
+      <c r="H1" s="180" t="n"/>
+      <c r="I1" s="180" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="166" t="inlineStr">
         <is>
@@ -45597,7 +45955,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
+++ b/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
@@ -22388,7 +22388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -22409,14 +22409,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -22795,7 +22787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -22816,14 +22808,6 @@
           <t>KAPAK — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -22959,7 +22943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC205"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22983,17 +22967,6 @@
           <t>ENVANTER — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
-      <c r="J1" s="180" t="n"/>
-      <c r="K1" s="180" t="n"/>
-      <c r="L1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -28473,7 +28446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28494,14 +28467,6 @@
           <t>DEGERLENDIRME — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -29999,7 +29964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC205"/>
+  <dimension ref="A1:Q205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5" customWidth="1" min="1" max="1"/>
@@ -30028,22 +29993,6 @@
           <t>EYLEM PLANI — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
-      <c r="J1" s="180" t="n"/>
-      <c r="K1" s="180" t="n"/>
-      <c r="L1" s="180" t="n"/>
-      <c r="M1" s="180" t="n"/>
-      <c r="N1" s="180" t="n"/>
-      <c r="O1" s="180" t="n"/>
-      <c r="P1" s="180" t="n"/>
-      <c r="Q1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -38562,7 +38511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45.5" customWidth="1" min="1" max="1"/>
@@ -38583,14 +38532,6 @@
           <t>AKIS — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -38751,7 +38692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="226.5" customWidth="1" min="1" max="1"/>
@@ -38772,14 +38713,6 @@
           <t>KANIT RAPORU — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -39166,7 +39099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -39187,14 +39120,6 @@
           <t>KONTROLLER — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -39453,7 +39378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -39474,14 +39399,6 @@
           <t>ORNEK VERI — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -39542,7 +39459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -39564,15 +39481,6 @@
           <t>LISTELER — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
-      <c r="J1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -39818,7 +39726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.5" customWidth="1" min="1" max="1"/>
@@ -39839,14 +39747,6 @@
           <t>AYARLAR — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -41288,7 +41188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -41419,7 +41319,7 @@
       <c r="I7" s="73" t="n"/>
       <c r="J7" s="73" t="n"/>
       <c r="K7" s="84">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="73" t="n"/>
@@ -41724,11 +41624,11 @@
         </is>
       </c>
       <c r="I19" s="173">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="174">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="98" t="inlineStr"/>
@@ -41875,7 +41775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="213.5" customWidth="1" min="1" max="1"/>
@@ -41896,14 +41796,6 @@
           <t>KILAVUZ — İSG Risk Değerlendirme Pro (6331)</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -42065,7 +41957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -42529,7 +42421,7 @@
         </is>
       </c>
       <c r="E17" s="131">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -42552,7 +42444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -42719,7 +42611,7 @@
       <c r="C11" s="73" t="n"/>
       <c r="D11" s="73" t="n"/>
       <c r="E11" s="178">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="73" t="n"/>
@@ -42876,7 +42768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -42897,14 +42789,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -43379,7 +43263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -43400,14 +43284,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -44134,7 +44010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" min="1" max="1"/>
@@ -44155,14 +44031,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -44820,7 +44688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -44841,14 +44709,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -45378,7 +45238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -45399,14 +45259,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="180" t="n"/>
-      <c r="C1" s="180" t="n"/>
-      <c r="D1" s="180" t="n"/>
-      <c r="E1" s="180" t="n"/>
-      <c r="F1" s="180" t="n"/>
-      <c r="G1" s="180" t="n"/>
-      <c r="H1" s="180" t="n"/>
-      <c r="I1" s="180" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">

--- a/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
+++ b/EXCELARSIV_PRODUCTS/isg-risk-degerlendirme-pro-6331/IsgRiskDegerlendirmePro6331.xlsx
@@ -109,7 +109,7 @@
     <numFmt numFmtId="170" formatCode="₺#,##0"/>
     <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="86">
+  <fonts count="121">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -603,8 +603,214 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -796,8 +1002,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1160,11 +1390,353 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1611,6 +2183,235 @@
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="18" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="18" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="89" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="91" fillId="18" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="89" fillId="18" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="18" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="95" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="39" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="64" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="97" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="39" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="64" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="103" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="104" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="17" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="107" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="107" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="12" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="11" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="115" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="106" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="117" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="117" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="12" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="11" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22410,7 +23211,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="146" t="inlineStr">
         <is>
@@ -22675,7 +23475,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="149" t="inlineStr">
         <is>
@@ -22809,7 +23608,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="198" t="inlineStr">
         <is>
@@ -22824,7 +23622,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -22867,7 +23664,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -22896,7 +23692,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -22911,7 +23706,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -22968,7 +23762,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="199" t="inlineStr">
         <is>
@@ -28468,7 +29261,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="199" t="inlineStr">
         <is>
@@ -28476,7 +29268,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
@@ -29374,9 +30165,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
@@ -29439,7 +30227,6 @@
         <v/>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
@@ -29994,7 +30781,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="199" t="inlineStr">
         <is>
@@ -30002,7 +30788,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
@@ -38533,7 +39318,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="199" t="inlineStr">
         <is>
@@ -38541,7 +39325,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
@@ -38582,7 +39365,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
@@ -38645,7 +39427,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
@@ -38714,7 +39495,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="198" t="inlineStr">
         <is>
@@ -38792,7 +39572,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
@@ -38914,7 +39693,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
@@ -38929,7 +39707,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
@@ -38950,7 +39727,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
@@ -38993,7 +39769,6 @@
       </c>
       <c r="B34" s="26" t="inlineStr"/>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="40" t="inlineStr">
         <is>
@@ -39001,7 +39776,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
@@ -39121,7 +39895,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="200" t="inlineStr">
         <is>
@@ -39129,7 +39902,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -39400,7 +40172,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="200" t="inlineStr">
         <is>
@@ -39415,7 +40186,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
@@ -39430,7 +40200,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
@@ -39482,7 +40251,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
@@ -39510,8 +40278,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
@@ -39748,7 +40514,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="199" t="inlineStr">
         <is>
@@ -39756,7 +40521,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
@@ -40521,8 +41285,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="H32" s="5" t="inlineStr">
         <is>
@@ -40674,8 +41436,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="H41" s="16" t="inlineStr">
         <is>
@@ -40970,7 +41730,6 @@
         <v/>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="H69" s="16" t="inlineStr">
         <is>
@@ -41191,554 +41950,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="68.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
-    <col width="36.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11.5" customWidth="1" min="7" max="7"/>
-    <col width="75.5" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="81.5" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="201" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="68" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="202" t="inlineStr">
         <is>
           <t>İSG RISK DEĞERLENDIRME PRO (6331)</t>
         </is>
       </c>
-      <c r="L2" s="69" t="inlineStr">
+      <c r="L2" s="203" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="70" t="inlineStr">
+      <c r="M2" s="204" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="71" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="205" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: İSG uzmanı, işveren vekili, denetim hazırlığı · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="72" t="inlineStr">
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="206" t="inlineStr">
         <is>
           <t>SENARYO</t>
         </is>
       </c>
-      <c r="C5" s="73" t="n"/>
-      <c r="D5" s="74" t="inlineStr">
+      <c r="C5" s="207" t="n"/>
+      <c r="D5" s="208" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="75" t="inlineStr">
+      <c r="E5" s="209" t="inlineStr">
         <is>
           <t>EYLEM YAŞLANDIRMA</t>
         </is>
       </c>
-      <c r="F5" s="73" t="n"/>
-      <c r="G5" s="76" t="inlineStr">
+      <c r="F5" s="207" t="n"/>
+      <c r="G5" s="210" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="72" t="inlineStr">
+      <c r="H5" s="211" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="73" t="n"/>
-      <c r="J5" s="77" t="inlineStr">
+      <c r="I5" s="207" t="n"/>
+      <c r="J5" s="212" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="78" t="inlineStr">
+      <c r="K5" s="213" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="73" t="n"/>
-      <c r="M5" s="74" t="inlineStr">
+      <c r="L5" s="207" t="n"/>
+      <c r="M5" s="214" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="79" t="n"/>
-      <c r="C6" s="73" t="n"/>
-      <c r="D6" s="73" t="n"/>
-      <c r="E6" s="80" t="n"/>
-      <c r="F6" s="73" t="n"/>
-      <c r="G6" s="73" t="n"/>
-      <c r="H6" s="79" t="n"/>
-      <c r="I6" s="73" t="n"/>
-      <c r="J6" s="73" t="n"/>
-      <c r="K6" s="81" t="n"/>
-      <c r="L6" s="73" t="n"/>
-      <c r="M6" s="73" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="169">
+    <row r="6" ht="6" customHeight="1">
+      <c r="B6" s="215" t="n"/>
+      <c r="C6" s="216" t="n"/>
+      <c r="D6" s="217" t="n"/>
+      <c r="E6" s="218" t="n"/>
+      <c r="F6" s="216" t="n"/>
+      <c r="G6" s="217" t="n"/>
+      <c r="H6" s="219" t="n"/>
+      <c r="I6" s="216" t="n"/>
+      <c r="J6" s="217" t="n"/>
+      <c r="K6" s="220" t="n"/>
+      <c r="L6" s="216" t="n"/>
+      <c r="M6" s="217" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="221">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="73" t="n"/>
-      <c r="D7" s="73" t="n"/>
-      <c r="E7" s="170">
+      <c r="C7" s="216" t="n"/>
+      <c r="D7" s="217" t="n"/>
+      <c r="E7" s="222">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="73" t="n"/>
-      <c r="G7" s="73" t="n"/>
-      <c r="H7" s="169">
+      <c r="F7" s="216" t="n"/>
+      <c r="G7" s="217" t="n"/>
+      <c r="H7" s="223">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="73" t="n"/>
-      <c r="J7" s="73" t="n"/>
-      <c r="K7" s="84">
+      <c r="I7" s="216" t="n"/>
+      <c r="J7" s="217" t="n"/>
+      <c r="K7" s="224">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="73" t="n"/>
-      <c r="M7" s="73" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="79" t="n"/>
-      <c r="C8" s="73" t="n"/>
-      <c r="D8" s="73" t="n"/>
-      <c r="E8" s="80" t="n"/>
-      <c r="F8" s="73" t="n"/>
-      <c r="G8" s="73" t="n"/>
-      <c r="H8" s="79" t="n"/>
-      <c r="I8" s="73" t="n"/>
-      <c r="J8" s="73" t="n"/>
-      <c r="K8" s="81" t="n"/>
-      <c r="L8" s="73" t="n"/>
-      <c r="M8" s="73" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="85" t="inlineStr">
+      <c r="L7" s="216" t="n"/>
+      <c r="M7" s="217" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="B8" s="215" t="n"/>
+      <c r="C8" s="216" t="n"/>
+      <c r="D8" s="217" t="n"/>
+      <c r="E8" s="218" t="n"/>
+      <c r="F8" s="216" t="n"/>
+      <c r="G8" s="217" t="n"/>
+      <c r="H8" s="219" t="n"/>
+      <c r="I8" s="216" t="n"/>
+      <c r="J8" s="217" t="n"/>
+      <c r="K8" s="220" t="n"/>
+      <c r="L8" s="216" t="n"/>
+      <c r="M8" s="217" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="225" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="73" t="n"/>
-      <c r="D9" s="73" t="n"/>
-      <c r="E9" s="86" t="inlineStr">
+      <c r="C9" s="226" t="n"/>
+      <c r="D9" s="227" t="n"/>
+      <c r="E9" s="228" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="73" t="n"/>
-      <c r="G9" s="73" t="n"/>
-      <c r="H9" s="85" t="inlineStr">
+      <c r="F9" s="226" t="n"/>
+      <c r="G9" s="227" t="n"/>
+      <c r="H9" s="229" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="73" t="n"/>
-      <c r="J9" s="73" t="n"/>
-      <c r="K9" s="87" t="inlineStr">
+      <c r="I9" s="226" t="n"/>
+      <c r="J9" s="227" t="n"/>
+      <c r="K9" s="230" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="73" t="n"/>
-      <c r="M9" s="73" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="66" t="inlineStr">
+      <c r="L9" s="226" t="n"/>
+      <c r="M9" s="227" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="231" t="inlineStr">
         <is>
           <t>İSG RISK DEĞERLENDIRME PRO (6331) — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="88" t="inlineStr">
+      <c r="F11" s="232" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="66" t="inlineStr">
+      <c r="H11" s="231" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="65" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="65" t="inlineStr">
+      <c r="H12" s="71" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="89" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="233" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="89" t="inlineStr">
+      <c r="C14" s="233" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="89" t="inlineStr">
+      <c r="D14" s="233" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="89" t="inlineStr">
+      <c r="E14" s="233" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="90" t="inlineStr">
+      <c r="H14" s="234" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="90" t="inlineStr">
+      <c r="I14" s="235" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="90" t="inlineStr">
+      <c r="J14" s="235" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="90" t="inlineStr">
+      <c r="K14" s="235" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="90" t="inlineStr">
+      <c r="L14" s="235" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="65" t="inlineStr">
+      <c r="M14" s="235" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="236" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="65" t="n">
+      <c r="C15" s="236" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="65" t="n">
+      <c r="D15" s="236" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="65" t="n">
+      <c r="E15" s="236" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="91" t="inlineStr">
+      <c r="H15" s="237" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="238">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="239">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="93" t="inlineStr">
+      <c r="K15" s="240" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="77" t="inlineStr">
+      <c r="L15" s="241" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="65" t="inlineStr">
+      <c r="M15" s="242" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="243" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="65" t="n">
+      <c r="C16" s="243" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="65" t="n">
+      <c r="D16" s="243" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="65" t="n">
+      <c r="E16" s="243" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="91" t="inlineStr">
+      <c r="H16" s="244" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="171">
+      <c r="I16" s="245">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="172">
+      <c r="J16" s="246">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="93" t="inlineStr">
+      <c r="K16" s="247" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="74" t="inlineStr">
+      <c r="L16" s="248" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="65" t="inlineStr">
+      <c r="M16" s="249" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="236" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="65" t="n">
+      <c r="C17" s="236" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="65" t="n">
+      <c r="D17" s="236" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="65" t="n">
+      <c r="E17" s="236" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="91" t="inlineStr">
+      <c r="H17" s="237" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="171">
+      <c r="I17" s="238">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="172">
+      <c r="J17" s="239">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="93" t="inlineStr">
+      <c r="K17" s="240" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="94" t="inlineStr">
+      <c r="L17" s="250" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="65" t="inlineStr">
+      <c r="M17" s="242" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="243" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="65" t="n">
+      <c r="C18" s="243" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="65" t="n">
+      <c r="D18" s="243" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="65" t="n">
+      <c r="E18" s="243" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="91" t="inlineStr">
+      <c r="H18" s="244" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="171">
+      <c r="I18" s="245">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="172">
+      <c r="J18" s="246">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="93" t="inlineStr">
+      <c r="K18" s="247" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="77" t="inlineStr">
+      <c r="L18" s="251" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="65" t="inlineStr">
+      <c r="M18" s="249" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="236" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="65" t="n">
+      <c r="C19" s="236" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="65" t="n">
+      <c r="D19" s="236" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="65" t="n">
+      <c r="E19" s="236" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="95" t="inlineStr">
+      <c r="H19" s="252" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="173">
+      <c r="I19" s="253">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="174">
+      <c r="J19" s="254">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="98" t="inlineStr"/>
-      <c r="L19" s="99" t="inlineStr">
+      <c r="K19" s="255" t="inlineStr"/>
+      <c r="L19" s="256" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="65" t="inlineStr">
+      <c r="M19" s="256" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="243" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="65" t="n">
+      <c r="C20" s="243" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="65" t="n">
+      <c r="D20" s="243" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="65" t="n">
+      <c r="E20" s="243" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="100" t="inlineStr">
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="257" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="100" t="inlineStr">
+      <c r="C22" s="207" t="n"/>
+      <c r="D22" s="207" t="n"/>
+      <c r="E22" s="258" t="n"/>
+      <c r="F22" s="257" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="101" t="inlineStr">
+      <c r="G22" s="207" t="n"/>
+      <c r="H22" s="207" t="n"/>
+      <c r="I22" s="258" t="n"/>
+      <c r="K22" s="259" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="102" t="n"/>
-      <c r="M22" s="102" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="50" t="inlineStr">
+      <c r="L22" s="260" t="n"/>
+      <c r="M22" s="261" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="262" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="65" t="inlineStr">
+      <c r="C23" s="216" t="n"/>
+      <c r="D23" s="216" t="n"/>
+      <c r="E23" s="217" t="n"/>
+      <c r="F23" s="263" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="103" t="inlineStr">
+      <c r="G23" s="216" t="n"/>
+      <c r="H23" s="216" t="n"/>
+      <c r="I23" s="264" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="104" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="102" t="n"/>
-      <c r="M23" s="102" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="51" t="inlineStr">
+      <c r="K23" s="265" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="266" t="n"/>
+      <c r="M23" s="267" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="268" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="65" t="inlineStr">
+      <c r="C24" s="216" t="n"/>
+      <c r="D24" s="216" t="n"/>
+      <c r="E24" s="217" t="n"/>
+      <c r="F24" s="263" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="103" t="inlineStr">
+      <c r="G24" s="216" t="n"/>
+      <c r="H24" s="216" t="n"/>
+      <c r="I24" s="264" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="105" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="106" t="inlineStr">
+      <c r="K24" s="269" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="270" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="50" t="inlineStr">
+      <c r="C25" s="216" t="n"/>
+      <c r="D25" s="216" t="n"/>
+      <c r="E25" s="217" t="n"/>
+      <c r="F25" s="241" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="107" t="inlineStr">
+      <c r="G25" s="271" t="n"/>
+      <c r="H25" s="271" t="n"/>
+      <c r="I25" s="271" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="272" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="108" t="inlineStr">
+      <c r="C26" s="216" t="n"/>
+      <c r="D26" s="216" t="n"/>
+      <c r="E26" s="217" t="n"/>
+      <c r="F26" s="273" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -41746,23 +42536,29 @@
       <c r="G26" s="181" t="n"/>
       <c r="H26" s="181" t="n"/>
       <c r="I26" s="182" t="n"/>
-      <c r="K26" s="109" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="274" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="275" t="n"/>
+      <c r="C27" s="226" t="n"/>
+      <c r="D27" s="226" t="n"/>
+      <c r="E27" s="227" t="n"/>
       <c r="F27" s="183" t="n"/>
       <c r="G27" s="184" t="n"/>
       <c r="H27" s="184" t="n"/>
       <c r="I27" s="185" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41797,7 +42593,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="200" t="inlineStr">
         <is>
@@ -41805,7 +42600,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
@@ -41979,7 +42773,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="110" t="inlineStr">
         <is>
@@ -42000,7 +42793,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="113" t="inlineStr">
         <is>
@@ -42413,7 +43205,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="130" t="inlineStr">
         <is>
@@ -42444,54 +43235,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="201" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="132" t="inlineStr">
         <is>
           <t>İSG RISK DEĞERLENDIRME PRO (6331) — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="133" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="276" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · İSG uzmanı, işveren vekili, denetim hazırlığı</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="134" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="277" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="135" t="inlineStr">
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="278" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -42500,7 +43292,7 @@
       <c r="D6" s="186" t="n"/>
       <c r="E6" s="186" t="n"/>
       <c r="F6" s="187" t="n"/>
-      <c r="H6" s="136" t="inlineStr">
+      <c r="H6" s="279" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -42510,151 +43302,151 @@
       <c r="K6" s="186" t="n"/>
       <c r="L6" s="187" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="73" t="n"/>
-      <c r="C7" s="73" t="n"/>
-      <c r="D7" s="73" t="n"/>
-      <c r="E7" s="73" t="n"/>
-      <c r="F7" s="73" t="n"/>
-      <c r="H7" s="73" t="n"/>
-      <c r="I7" s="73" t="n"/>
-      <c r="J7" s="73" t="n"/>
-      <c r="K7" s="73" t="n"/>
-      <c r="L7" s="73" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="137" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="280" t="n"/>
+      <c r="C7" s="216" t="n"/>
+      <c r="D7" s="216" t="n"/>
+      <c r="E7" s="216" t="n"/>
+      <c r="F7" s="281" t="n"/>
+      <c r="H7" s="282" t="n"/>
+      <c r="I7" s="216" t="n"/>
+      <c r="J7" s="216" t="n"/>
+      <c r="K7" s="216" t="n"/>
+      <c r="L7" s="283" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="284" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="73" t="n"/>
-      <c r="D8" s="73" t="n"/>
-      <c r="E8" s="138" t="inlineStr">
+      <c r="C8" s="216" t="n"/>
+      <c r="D8" s="216" t="n"/>
+      <c r="E8" s="285" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="73" t="n"/>
-      <c r="H8" s="137" t="inlineStr">
+      <c r="F8" s="281" t="n"/>
+      <c r="H8" s="286" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="73" t="n"/>
-      <c r="J8" s="73" t="n"/>
-      <c r="K8" s="139" t="inlineStr">
+      <c r="I8" s="216" t="n"/>
+      <c r="J8" s="216" t="n"/>
+      <c r="K8" s="287" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="73" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="137" t="inlineStr">
+      <c r="L8" s="283" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="284" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="73" t="n"/>
-      <c r="D9" s="73" t="n"/>
-      <c r="E9" s="176">
+      <c r="C9" s="216" t="n"/>
+      <c r="D9" s="216" t="n"/>
+      <c r="E9" s="288">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="73" t="n"/>
-      <c r="H9" s="137" t="inlineStr">
+      <c r="F9" s="281" t="n"/>
+      <c r="H9" s="286" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="73" t="n"/>
-      <c r="J9" s="73" t="n"/>
-      <c r="K9" s="176">
+      <c r="I9" s="216" t="n"/>
+      <c r="J9" s="216" t="n"/>
+      <c r="K9" s="288">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="73" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="137" t="inlineStr">
+      <c r="L9" s="283" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="284" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="73" t="n"/>
-      <c r="D10" s="73" t="n"/>
-      <c r="E10" s="177">
+      <c r="C10" s="216" t="n"/>
+      <c r="D10" s="216" t="n"/>
+      <c r="E10" s="289">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="73" t="n"/>
-      <c r="H10" s="137" t="inlineStr">
+      <c r="F10" s="281" t="n"/>
+      <c r="H10" s="286" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="73" t="n"/>
-      <c r="J10" s="73" t="n"/>
-      <c r="K10" s="177">
+      <c r="I10" s="216" t="n"/>
+      <c r="J10" s="216" t="n"/>
+      <c r="K10" s="289">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="73" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="137" t="inlineStr">
+      <c r="L10" s="283" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="284" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="73" t="n"/>
-      <c r="D11" s="73" t="n"/>
-      <c r="E11" s="178">
+      <c r="C11" s="216" t="n"/>
+      <c r="D11" s="216" t="n"/>
+      <c r="E11" s="290">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="73" t="n"/>
-      <c r="H11" s="137" t="inlineStr">
+      <c r="F11" s="281" t="n"/>
+      <c r="H11" s="286" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="73" t="n"/>
-      <c r="J11" s="73" t="n"/>
-      <c r="K11" s="141" t="inlineStr">
+      <c r="I11" s="216" t="n"/>
+      <c r="J11" s="216" t="n"/>
+      <c r="K11" s="291" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="73" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="73" t="n"/>
-      <c r="C12" s="73" t="n"/>
-      <c r="D12" s="73" t="n"/>
-      <c r="E12" s="73" t="n"/>
-      <c r="F12" s="73" t="n"/>
-      <c r="H12" s="73" t="n"/>
-      <c r="I12" s="73" t="n"/>
-      <c r="J12" s="73" t="n"/>
-      <c r="K12" s="73" t="n"/>
-      <c r="L12" s="73" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="73" t="n"/>
-      <c r="C13" s="73" t="n"/>
-      <c r="D13" s="73" t="n"/>
-      <c r="E13" s="73" t="n"/>
-      <c r="F13" s="73" t="n"/>
-      <c r="H13" s="73" t="n"/>
-      <c r="I13" s="73" t="n"/>
-      <c r="J13" s="73" t="n"/>
-      <c r="K13" s="73" t="n"/>
-      <c r="L13" s="73" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="142" t="inlineStr">
+      <c r="L11" s="283" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="280" t="n"/>
+      <c r="C12" s="216" t="n"/>
+      <c r="D12" s="216" t="n"/>
+      <c r="E12" s="216" t="n"/>
+      <c r="F12" s="281" t="n"/>
+      <c r="H12" s="282" t="n"/>
+      <c r="I12" s="216" t="n"/>
+      <c r="J12" s="216" t="n"/>
+      <c r="K12" s="216" t="n"/>
+      <c r="L12" s="283" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="280" t="n"/>
+      <c r="C13" s="216" t="n"/>
+      <c r="D13" s="216" t="n"/>
+      <c r="E13" s="216" t="n"/>
+      <c r="F13" s="281" t="n"/>
+      <c r="H13" s="282" t="n"/>
+      <c r="I13" s="216" t="n"/>
+      <c r="J13" s="216" t="n"/>
+      <c r="K13" s="216" t="n"/>
+      <c r="L13" s="283" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="292" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -42663,7 +43455,7 @@
       <c r="D14" s="188" t="n"/>
       <c r="E14" s="188" t="n"/>
       <c r="F14" s="189" t="n"/>
-      <c r="H14" s="143" t="inlineStr">
+      <c r="H14" s="293" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -42673,7 +43465,7 @@
       <c r="K14" s="190" t="n"/>
       <c r="L14" s="191" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="192" t="n"/>
       <c r="C15" s="193" t="n"/>
       <c r="D15" s="193" t="n"/>
@@ -42685,70 +43477,185 @@
       <c r="K15" s="196" t="n"/>
       <c r="L15" s="197" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="53" t="inlineStr">
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="294" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="100" t="inlineStr">
+      <c r="C17" s="207" t="n"/>
+      <c r="D17" s="207" t="n"/>
+      <c r="E17" s="207" t="n"/>
+      <c r="F17" s="207" t="n"/>
+      <c r="G17" s="207" t="n"/>
+      <c r="H17" s="207" t="n"/>
+      <c r="I17" s="207" t="n"/>
+      <c r="J17" s="207" t="n"/>
+      <c r="K17" s="207" t="n"/>
+      <c r="L17" s="258" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="295" t="n"/>
+      <c r="C18" s="216" t="n"/>
+      <c r="D18" s="216" t="n"/>
+      <c r="E18" s="216" t="n"/>
+      <c r="F18" s="216" t="n"/>
+      <c r="G18" s="216" t="n"/>
+      <c r="H18" s="216" t="n"/>
+      <c r="I18" s="216" t="n"/>
+      <c r="J18" s="216" t="n"/>
+      <c r="K18" s="216" t="n"/>
+      <c r="L18" s="217" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="296" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="144" t="inlineStr">
+      <c r="C19" s="216" t="n"/>
+      <c r="D19" s="216" t="n"/>
+      <c r="E19" s="216" t="n"/>
+      <c r="F19" s="216" t="n"/>
+      <c r="G19" s="216" t="n"/>
+      <c r="H19" s="216" t="n"/>
+      <c r="I19" s="216" t="n"/>
+      <c r="J19" s="216" t="n"/>
+      <c r="K19" s="216" t="n"/>
+      <c r="L19" s="217" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="297" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="100" t="inlineStr">
+      <c r="C20" s="216" t="n"/>
+      <c r="D20" s="216" t="n"/>
+      <c r="E20" s="216" t="n"/>
+      <c r="F20" s="216" t="n"/>
+      <c r="G20" s="216" t="n"/>
+      <c r="H20" s="216" t="n"/>
+      <c r="I20" s="216" t="n"/>
+      <c r="J20" s="216" t="n"/>
+      <c r="K20" s="216" t="n"/>
+      <c r="L20" s="217" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="296" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="144" t="inlineStr">
+      <c r="C21" s="216" t="n"/>
+      <c r="D21" s="216" t="n"/>
+      <c r="E21" s="216" t="n"/>
+      <c r="F21" s="216" t="n"/>
+      <c r="G21" s="216" t="n"/>
+      <c r="H21" s="216" t="n"/>
+      <c r="I21" s="216" t="n"/>
+      <c r="J21" s="216" t="n"/>
+      <c r="K21" s="216" t="n"/>
+      <c r="L21" s="217" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="297" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="100" t="inlineStr">
+      <c r="C22" s="216" t="n"/>
+      <c r="D22" s="216" t="n"/>
+      <c r="E22" s="216" t="n"/>
+      <c r="F22" s="216" t="n"/>
+      <c r="G22" s="216" t="n"/>
+      <c r="H22" s="216" t="n"/>
+      <c r="I22" s="216" t="n"/>
+      <c r="J22" s="216" t="n"/>
+      <c r="K22" s="216" t="n"/>
+      <c r="L22" s="217" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="296" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="144" t="inlineStr">
+      <c r="C23" s="216" t="n"/>
+      <c r="D23" s="216" t="n"/>
+      <c r="E23" s="216" t="n"/>
+      <c r="F23" s="216" t="n"/>
+      <c r="G23" s="216" t="n"/>
+      <c r="H23" s="216" t="n"/>
+      <c r="I23" s="216" t="n"/>
+      <c r="J23" s="216" t="n"/>
+      <c r="K23" s="216" t="n"/>
+      <c r="L23" s="217" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="297" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="100" t="inlineStr">
+      <c r="C24" s="216" t="n"/>
+      <c r="D24" s="216" t="n"/>
+      <c r="E24" s="216" t="n"/>
+      <c r="F24" s="216" t="n"/>
+      <c r="G24" s="216" t="n"/>
+      <c r="H24" s="216" t="n"/>
+      <c r="I24" s="216" t="n"/>
+      <c r="J24" s="216" t="n"/>
+      <c r="K24" s="216" t="n"/>
+      <c r="L24" s="217" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="296" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="144" t="inlineStr">
+      <c r="C25" s="216" t="n"/>
+      <c r="D25" s="216" t="n"/>
+      <c r="E25" s="216" t="n"/>
+      <c r="F25" s="216" t="n"/>
+      <c r="G25" s="216" t="n"/>
+      <c r="H25" s="216" t="n"/>
+      <c r="I25" s="216" t="n"/>
+      <c r="J25" s="216" t="n"/>
+      <c r="K25" s="216" t="n"/>
+      <c r="L25" s="217" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="297" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="216" t="n"/>
+      <c r="D26" s="216" t="n"/>
+      <c r="E26" s="216" t="n"/>
+      <c r="F26" s="216" t="n"/>
+      <c r="G26" s="216" t="n"/>
+      <c r="H26" s="216" t="n"/>
+      <c r="I26" s="216" t="n"/>
+      <c r="J26" s="216" t="n"/>
+      <c r="K26" s="216" t="n"/>
+      <c r="L26" s="217" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="275" t="n"/>
+      <c r="C27" s="226" t="n"/>
+      <c r="D27" s="226" t="n"/>
+      <c r="E27" s="226" t="n"/>
+      <c r="F27" s="226" t="n"/>
+      <c r="G27" s="226" t="n"/>
+      <c r="H27" s="226" t="n"/>
+      <c r="I27" s="226" t="n"/>
+      <c r="J27" s="226" t="n"/>
+      <c r="K27" s="226" t="n"/>
+      <c r="L27" s="227" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -42790,7 +43697,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="151" t="inlineStr">
         <is>
@@ -43285,7 +44191,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="154" t="inlineStr">
         <is>
@@ -44032,7 +44937,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="159" t="inlineStr">
         <is>
@@ -44710,7 +45614,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="163" t="inlineStr">
         <is>
@@ -45260,7 +46163,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="166" t="inlineStr">
         <is>
